--- a/rawresource/excels/attribute.xlsx
+++ b/rawresource/excels/attribute.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\MServer\rawresource\excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="22188" windowHeight="9180" tabRatio="500"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>attr_base_conf</t>
   </si>
@@ -44,7 +49,10 @@
     <t>属性名字</t>
   </si>
   <si>
-    <t>num</t>
+    <t>int</t>
+  </si>
+  <si>
+    <t>double</t>
   </si>
   <si>
     <t>str</t>
@@ -1305,10 +1313,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -1316,13 +1324,13 @@
     <row r="4" spans="1:6">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -1330,13 +1338,13 @@
     <row r="5" spans="1:6">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -1349,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1360,7 +1368,7 @@
         <v>2.5</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1371,7 +1379,7 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1382,7 +1390,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
